--- a/data/P1/P1T3_BQ6.xlsx
+++ b/data/P1/P1T3_BQ6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD461AC-9684-B24A-88FD-187F19F03090}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9993999-E5AE-F64B-B2E5-00BEF754FF72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -238,13 +238,115 @@
   </si>
   <si>
     <t>老師幫助我們學習。</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/kaʊ/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/mɪlk/</t>
+  </si>
+  <si>
+    <t>/ˈmɑːkɪt/</t>
+  </si>
+  <si>
+    <t>mar-ket</t>
+  </si>
+  <si>
+    <t>/baɪ/</t>
+  </si>
+  <si>
+    <t>/pleɪn/</t>
+  </si>
+  <si>
+    <t>/ˈfænsi/</t>
+  </si>
+  <si>
+    <t>fan-cy</t>
+  </si>
+  <si>
+    <t>/ˈkɒmɪk bʊk/</t>
+  </si>
+  <si>
+    <t>com-ic book</t>
+  </si>
+  <si>
+    <t>/bɔːd ɡeɪm/</t>
+  </si>
+  <si>
+    <t>/ˈstɪkəz/</t>
+  </si>
+  <si>
+    <t>stick-ers</t>
+  </si>
+  <si>
+    <t>/pɪnz/</t>
+  </si>
+  <si>
+    <t>/stæmps/</t>
+  </si>
+  <si>
+    <t>/ˈbjuːtɪfl/</t>
+  </si>
+  <si>
+    <t>beau-ti-ful</t>
+  </si>
+  <si>
+    <t>/ɪkˈsaɪtɪd/</t>
+  </si>
+  <si>
+    <t>ex-ci-ted</t>
+  </si>
+  <si>
+    <t>/sæd/</t>
+  </si>
+  <si>
+    <t>/ˈæŋɡri/</t>
+  </si>
+  <si>
+    <t>an-gry</t>
+  </si>
+  <si>
+    <t>/pəˈliːs ˈɒfɪsə(r)/</t>
+  </si>
+  <si>
+    <t>po-lice-of-fi-cer</t>
+  </si>
+  <si>
+    <t>/ˈsniːkəz/</t>
+  </si>
+  <si>
+    <t>sneak-ers</t>
+  </si>
+  <si>
+    <t>/dres/</t>
+  </si>
+  <si>
+    <t>/ˈmʌni/</t>
+  </si>
+  <si>
+    <t>mon-ey</t>
+  </si>
+  <si>
+    <t>/ˈsuːpəmɑːkɪt/</t>
+  </si>
+  <si>
+    <t>su-per-mar-ket</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -287,6 +389,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -296,12 +406,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -310,7 +435,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -324,6 +449,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -644,6 +772,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -656,8 +787,15 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="D1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
@@ -669,8 +807,12 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
@@ -682,6 +824,12 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
@@ -693,6 +841,12 @@
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
@@ -704,6 +858,12 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
@@ -715,6 +875,12 @@
       <c r="C6">
         <v>1</v>
       </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
@@ -726,6 +892,12 @@
       <c r="C7">
         <v>2</v>
       </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
@@ -737,6 +909,12 @@
       <c r="C8">
         <v>2</v>
       </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
@@ -748,6 +926,12 @@
       <c r="C9">
         <v>2</v>
       </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
@@ -759,6 +943,12 @@
       <c r="C10">
         <v>2</v>
       </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
@@ -770,6 +960,12 @@
       <c r="C11">
         <v>2</v>
       </c>
+      <c r="D11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
@@ -781,6 +977,12 @@
       <c r="C12">
         <v>3</v>
       </c>
+      <c r="D12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
@@ -792,6 +994,12 @@
       <c r="C13">
         <v>3</v>
       </c>
+      <c r="D13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
@@ -803,6 +1011,12 @@
       <c r="C14">
         <v>3</v>
       </c>
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
@@ -814,6 +1028,12 @@
       <c r="C15">
         <v>3</v>
       </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
@@ -825,8 +1045,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -836,8 +1062,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -847,8 +1079,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -858,8 +1096,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
@@ -869,8 +1113,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -880,20 +1130,26 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T3_BQ6.xlsx
+++ b/data/P1/P1T3_BQ6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9993999-E5AE-F64B-B2E5-00BEF754FF72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99603039-AC46-5947-B238-444AFCEA7C41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="32020" yWindow="1800" windowWidth="29160" windowHeight="18380" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="124">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -340,6 +340,70 @@
   </si>
   <si>
     <t>su-per-mar-ket</t>
+  </si>
+  <si>
+    <t>A big farm animal that gives us milk</t>
+  </si>
+  <si>
+    <t>White drink we get from cows</t>
+  </si>
+  <si>
+    <t>A place to buy food and small things</t>
+  </si>
+  <si>
+    <t>To get things by giving money</t>
+  </si>
+  <si>
+    <t>Simple, not bright or decorated</t>
+  </si>
+  <si>
+    <t>Pretty and special with nice designs</t>
+  </si>
+  <si>
+    <t>A book with funny pictures and short stories</t>
+  </si>
+  <si>
+    <t>A game played on a flat board with pieces</t>
+  </si>
+  <si>
+    <t>Small sticky pretty pictures you can put on things</t>
+  </si>
+  <si>
+    <t>Small sharp metal pieces to hold paper together</t>
+  </si>
+  <si>
+    <t>Small paper marks you put on letters to send them</t>
+  </si>
+  <si>
+    <t>Very pretty, nice to look at</t>
+  </si>
+  <si>
+    <t>Very happy and ready for fun things</t>
+  </si>
+  <si>
+    <t>Feeling unhappy</t>
+  </si>
+  <si>
+    <t>Feeling mad about something</t>
+  </si>
+  <si>
+    <t>A person who keeps people safe</t>
+  </si>
+  <si>
+    <t>Soft shoes for running and playing</t>
+  </si>
+  <si>
+    <t>A nice piece of clothes for girls</t>
+  </si>
+  <si>
+    <t>Coins or paper we use to buy things</t>
+  </si>
+  <si>
+    <t>A big shop with many kinds of food and goods</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -768,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -777,7 +841,7 @@
     <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -793,11 +857,12 @@
       <c r="E1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -813,8 +878,11 @@
       <c r="E2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="F2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -830,8 +898,11 @@
       <c r="E3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="F3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -847,8 +918,11 @@
       <c r="E4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -864,8 +938,11 @@
       <c r="E5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -881,8 +958,11 @@
       <c r="E6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -898,8 +978,11 @@
       <c r="E7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -915,8 +998,11 @@
       <c r="E8" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -932,8 +1018,11 @@
       <c r="E9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -949,8 +1038,11 @@
       <c r="E10" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -966,8 +1058,11 @@
       <c r="E11" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -983,8 +1078,11 @@
       <c r="E12" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -1000,8 +1098,11 @@
       <c r="E13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1017,8 +1118,11 @@
       <c r="E14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -1034,8 +1138,11 @@
       <c r="E15" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="F15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -1051,8 +1158,11 @@
       <c r="E16" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1068,8 +1178,11 @@
       <c r="E17" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -1085,8 +1198,11 @@
       <c r="E18" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1102,8 +1218,11 @@
       <c r="E19" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>23</v>
       </c>
@@ -1119,8 +1238,11 @@
       <c r="E20" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1136,20 +1258,23 @@
       <c r="E21" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
